--- a/research/traditional_assets/database/data/china/china_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/china/china_homebuilding.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07150000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="G2">
-        <v>0.2418629550321199</v>
+        <v>-0.9241535776614311</v>
       </c>
       <c r="H2">
-        <v>0.2184154175588865</v>
+        <v>-0.9389179755671903</v>
       </c>
       <c r="I2">
-        <v>-0.4925053533190578</v>
+        <v>-0.6858638743455497</v>
       </c>
       <c r="J2">
-        <v>-0.4925053533190578</v>
+        <v>-0.6858638743455497</v>
       </c>
       <c r="K2">
-        <v>-43.5</v>
+        <v>-33.8</v>
       </c>
       <c r="L2">
-        <v>-0.4657387580299786</v>
+        <v>-0.5898778359511344</v>
       </c>
       <c r="M2">
-        <v>6.75</v>
+        <v>7.37</v>
       </c>
       <c r="N2">
-        <v>0.01299326275264677</v>
+        <v>0.0155649419218585</v>
       </c>
       <c r="O2">
-        <v>-0.1551724137931035</v>
+        <v>-0.2180473372781065</v>
       </c>
       <c r="P2">
-        <v>6.75</v>
+        <v>7.37</v>
       </c>
       <c r="Q2">
-        <v>0.01299326275264677</v>
+        <v>0.0155649419218585</v>
       </c>
       <c r="R2">
-        <v>-0.1551724137931035</v>
+        <v>-0.2180473372781065</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>30.1</v>
+        <v>18.1</v>
       </c>
       <c r="V2">
-        <v>0.05794032723772859</v>
+        <v>0.0382259767687434</v>
       </c>
       <c r="W2">
-        <v>-0.1891304347826087</v>
+        <v>-0.1703629032258064</v>
       </c>
       <c r="X2">
-        <v>0.09795788850299056</v>
+        <v>0.12703118317905</v>
       </c>
       <c r="Y2">
-        <v>-0.2870883232855992</v>
+        <v>-0.2973940864048565</v>
       </c>
       <c r="Z2">
-        <v>0.2645892351274788</v>
+        <v>0.1555796904697258</v>
       </c>
       <c r="AA2">
-        <v>-0.1303116147308782</v>
+        <v>-0.1067064892750475</v>
       </c>
       <c r="AB2">
-        <v>0.07780656198697324</v>
+        <v>0.1064532904722251</v>
       </c>
       <c r="AC2">
-        <v>-0.2081181767178514</v>
+        <v>-0.2131597797472727</v>
       </c>
       <c r="AD2">
-        <v>200</v>
+        <v>165.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>200</v>
+        <v>165.9</v>
       </c>
       <c r="AG2">
-        <v>169.9</v>
+        <v>147.8</v>
       </c>
       <c r="AH2">
-        <v>0.2779708130646282</v>
+        <v>0.2594619956208946</v>
       </c>
       <c r="AI2">
-        <v>0.5020080321285141</v>
+        <v>0.5317307692307692</v>
       </c>
       <c r="AJ2">
-        <v>0.2464461850884828</v>
+        <v>0.2378882987284726</v>
       </c>
       <c r="AK2">
-        <v>0.4613087157208797</v>
+        <v>0.5028921401837361</v>
       </c>
       <c r="AL2">
-        <v>7.96</v>
+        <v>6.37</v>
       </c>
       <c r="AM2">
-        <v>7.647</v>
+        <v>6.125</v>
       </c>
       <c r="AN2">
-        <v>-6.896551724137931</v>
+        <v>-6.121771217712177</v>
       </c>
       <c r="AO2">
-        <v>-5.778894472361809</v>
+        <v>-6.169544740973312</v>
       </c>
       <c r="AP2">
-        <v>-5.858620689655172</v>
+        <v>-5.453874538745388</v>
       </c>
       <c r="AQ2">
-        <v>-6.015430887929907</v>
+        <v>-6.416326530612245</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07150000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="G3">
-        <v>0.2418629550321199</v>
+        <v>-0.9241535776614311</v>
       </c>
       <c r="H3">
-        <v>0.2184154175588865</v>
+        <v>-0.9389179755671903</v>
       </c>
       <c r="I3">
-        <v>-0.4925053533190578</v>
+        <v>-0.6858638743455497</v>
       </c>
       <c r="J3">
-        <v>-0.4925053533190578</v>
+        <v>-0.6858638743455497</v>
       </c>
       <c r="K3">
-        <v>-43.5</v>
+        <v>-33.8</v>
       </c>
       <c r="L3">
-        <v>-0.4657387580299786</v>
+        <v>-0.5898778359511344</v>
       </c>
       <c r="M3">
-        <v>6.75</v>
+        <v>7.37</v>
       </c>
       <c r="N3">
-        <v>0.01299326275264677</v>
+        <v>0.0155649419218585</v>
       </c>
       <c r="O3">
-        <v>-0.1551724137931035</v>
+        <v>-0.2180473372781065</v>
       </c>
       <c r="P3">
-        <v>6.75</v>
+        <v>7.37</v>
       </c>
       <c r="Q3">
-        <v>0.01299326275264677</v>
+        <v>0.0155649419218585</v>
       </c>
       <c r="R3">
-        <v>-0.1551724137931035</v>
+        <v>-0.2180473372781065</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>30.1</v>
+        <v>18.1</v>
       </c>
       <c r="V3">
-        <v>0.05794032723772859</v>
+        <v>0.0382259767687434</v>
       </c>
       <c r="W3">
-        <v>-0.1891304347826087</v>
+        <v>-0.1703629032258064</v>
       </c>
       <c r="X3">
-        <v>0.09795788850299056</v>
+        <v>0.12703118317905</v>
       </c>
       <c r="Y3">
-        <v>-0.2870883232855992</v>
+        <v>-0.2973940864048565</v>
       </c>
       <c r="Z3">
-        <v>0.2645892351274788</v>
+        <v>0.1555796904697258</v>
       </c>
       <c r="AA3">
-        <v>-0.1303116147308782</v>
+        <v>-0.1067064892750475</v>
       </c>
       <c r="AB3">
-        <v>0.07780656198697324</v>
+        <v>0.1064532904722251</v>
       </c>
       <c r="AC3">
-        <v>-0.2081181767178514</v>
+        <v>-0.2131597797472727</v>
       </c>
       <c r="AD3">
-        <v>200</v>
+        <v>165.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>200</v>
+        <v>165.9</v>
       </c>
       <c r="AG3">
-        <v>169.9</v>
+        <v>147.8</v>
       </c>
       <c r="AH3">
-        <v>0.2779708130646282</v>
+        <v>0.2594619956208946</v>
       </c>
       <c r="AI3">
-        <v>0.5020080321285141</v>
+        <v>0.5317307692307692</v>
       </c>
       <c r="AJ3">
-        <v>0.2464461850884828</v>
+        <v>0.2378882987284726</v>
       </c>
       <c r="AK3">
-        <v>0.4613087157208797</v>
+        <v>0.5028921401837361</v>
       </c>
       <c r="AL3">
-        <v>7.96</v>
+        <v>6.37</v>
       </c>
       <c r="AM3">
-        <v>7.647</v>
+        <v>6.125</v>
       </c>
       <c r="AN3">
-        <v>-6.896551724137931</v>
+        <v>-6.121771217712177</v>
       </c>
       <c r="AO3">
-        <v>-5.778894472361809</v>
+        <v>-6.169544740973312</v>
       </c>
       <c r="AP3">
-        <v>-5.858620689655172</v>
+        <v>-5.453874538745388</v>
       </c>
       <c r="AQ3">
-        <v>-6.015430887929907</v>
+        <v>-6.416326530612245</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/china/china_homebuilding.xlsx
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.2</v>
+        <v>0.0876</v>
       </c>
       <c r="G2">
-        <v>-0.9241535776614311</v>
+        <v>-0.08245989304812835</v>
       </c>
       <c r="H2">
-        <v>-0.9389179755671903</v>
+        <v>-0.09679144385026739</v>
       </c>
       <c r="I2">
-        <v>-0.6858638743455497</v>
+        <v>-0.1112299465240642</v>
       </c>
       <c r="J2">
-        <v>-0.6858638743455497</v>
+        <v>-0.1112299465240642</v>
       </c>
       <c r="K2">
-        <v>-33.8</v>
+        <v>-29.1</v>
       </c>
       <c r="L2">
-        <v>-0.5898778359511344</v>
+        <v>-0.1556149732620321</v>
       </c>
       <c r="M2">
-        <v>7.37</v>
+        <v>5.69</v>
       </c>
       <c r="N2">
-        <v>0.0155649419218585</v>
+        <v>0.01341664701721292</v>
       </c>
       <c r="O2">
-        <v>-0.2180473372781065</v>
+        <v>-0.19553264604811</v>
       </c>
       <c r="P2">
-        <v>7.37</v>
+        <v>5.69</v>
       </c>
       <c r="Q2">
-        <v>0.0155649419218585</v>
+        <v>0.01341664701721292</v>
       </c>
       <c r="R2">
-        <v>-0.2180473372781065</v>
+        <v>-0.19553264604811</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18.1</v>
+        <v>43.9</v>
       </c>
       <c r="V2">
-        <v>0.0382259767687434</v>
+        <v>0.1035133223296392</v>
       </c>
       <c r="W2">
-        <v>-0.1703629032258064</v>
+        <v>-0.1991786447638604</v>
       </c>
       <c r="X2">
-        <v>0.12703118317905</v>
+        <v>0.1105171760390992</v>
       </c>
       <c r="Y2">
-        <v>-0.2973940864048565</v>
+        <v>-0.3096958208029595</v>
       </c>
       <c r="Z2">
-        <v>0.1555796904697258</v>
+        <v>0.6362708404219123</v>
       </c>
       <c r="AA2">
-        <v>-0.1067064892750475</v>
+        <v>-0.07077237155495067</v>
       </c>
       <c r="AB2">
-        <v>0.1064532904722251</v>
+        <v>0.09062995838661299</v>
       </c>
       <c r="AC2">
-        <v>-0.2131597797472727</v>
+        <v>-0.1614023299415637</v>
       </c>
       <c r="AD2">
-        <v>165.9</v>
+        <v>180.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>165.9</v>
+        <v>180.5</v>
       </c>
       <c r="AG2">
-        <v>147.8</v>
+        <v>136.6</v>
       </c>
       <c r="AH2">
-        <v>0.2594619956208946</v>
+        <v>0.2985444922262653</v>
       </c>
       <c r="AI2">
-        <v>0.5317307692307692</v>
+        <v>0.608974358974359</v>
       </c>
       <c r="AJ2">
-        <v>0.2378882987284726</v>
+        <v>0.2436240413768503</v>
       </c>
       <c r="AK2">
-        <v>0.5028921401837361</v>
+        <v>0.5409900990099009</v>
       </c>
       <c r="AL2">
-        <v>6.37</v>
+        <v>6</v>
       </c>
       <c r="AM2">
-        <v>6.125</v>
+        <v>5.732</v>
       </c>
       <c r="AN2">
-        <v>-6.121771217712177</v>
+        <v>-17.87128712871287</v>
       </c>
       <c r="AO2">
-        <v>-6.169544740973312</v>
+        <v>-3.466666666666667</v>
       </c>
       <c r="AP2">
-        <v>-5.453874538745388</v>
+        <v>-13.52475247524752</v>
       </c>
       <c r="AQ2">
-        <v>-6.416326530612245</v>
+        <v>-3.628750872295883</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.2</v>
+        <v>0.0876</v>
       </c>
       <c r="G3">
-        <v>-0.9241535776614311</v>
+        <v>-0.08245989304812835</v>
       </c>
       <c r="H3">
-        <v>-0.9389179755671903</v>
+        <v>-0.09679144385026739</v>
       </c>
       <c r="I3">
-        <v>-0.6858638743455497</v>
+        <v>-0.1112299465240642</v>
       </c>
       <c r="J3">
-        <v>-0.6858638743455497</v>
+        <v>-0.1112299465240642</v>
       </c>
       <c r="K3">
-        <v>-33.8</v>
+        <v>-29.1</v>
       </c>
       <c r="L3">
-        <v>-0.5898778359511344</v>
+        <v>-0.1556149732620321</v>
       </c>
       <c r="M3">
-        <v>7.37</v>
+        <v>5.69</v>
       </c>
       <c r="N3">
-        <v>0.0155649419218585</v>
+        <v>0.01341664701721292</v>
       </c>
       <c r="O3">
-        <v>-0.2180473372781065</v>
+        <v>-0.19553264604811</v>
       </c>
       <c r="P3">
-        <v>7.37</v>
+        <v>5.69</v>
       </c>
       <c r="Q3">
-        <v>0.0155649419218585</v>
+        <v>0.01341664701721292</v>
       </c>
       <c r="R3">
-        <v>-0.2180473372781065</v>
+        <v>-0.19553264604811</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.1</v>
+        <v>43.9</v>
       </c>
       <c r="V3">
-        <v>0.0382259767687434</v>
+        <v>0.1035133223296392</v>
       </c>
       <c r="W3">
-        <v>-0.1703629032258064</v>
+        <v>-0.1991786447638604</v>
       </c>
       <c r="X3">
-        <v>0.12703118317905</v>
+        <v>0.1105171760390992</v>
       </c>
       <c r="Y3">
-        <v>-0.2973940864048565</v>
+        <v>-0.3096958208029595</v>
       </c>
       <c r="Z3">
-        <v>0.1555796904697258</v>
+        <v>0.6362708404219123</v>
       </c>
       <c r="AA3">
-        <v>-0.1067064892750475</v>
+        <v>-0.07077237155495067</v>
       </c>
       <c r="AB3">
-        <v>0.1064532904722251</v>
+        <v>0.09062995838661299</v>
       </c>
       <c r="AC3">
-        <v>-0.2131597797472727</v>
+        <v>-0.1614023299415637</v>
       </c>
       <c r="AD3">
-        <v>165.9</v>
+        <v>180.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>165.9</v>
+        <v>180.5</v>
       </c>
       <c r="AG3">
-        <v>147.8</v>
+        <v>136.6</v>
       </c>
       <c r="AH3">
-        <v>0.2594619956208946</v>
+        <v>0.2985444922262653</v>
       </c>
       <c r="AI3">
-        <v>0.5317307692307692</v>
+        <v>0.608974358974359</v>
       </c>
       <c r="AJ3">
-        <v>0.2378882987284726</v>
+        <v>0.2436240413768503</v>
       </c>
       <c r="AK3">
-        <v>0.5028921401837361</v>
+        <v>0.5409900990099009</v>
       </c>
       <c r="AL3">
-        <v>6.37</v>
+        <v>6</v>
       </c>
       <c r="AM3">
-        <v>6.125</v>
+        <v>5.732</v>
       </c>
       <c r="AN3">
-        <v>-6.121771217712177</v>
+        <v>-17.87128712871287</v>
       </c>
       <c r="AO3">
-        <v>-6.169544740973312</v>
+        <v>-3.466666666666667</v>
       </c>
       <c r="AP3">
-        <v>-5.453874538745388</v>
+        <v>-13.52475247524752</v>
       </c>
       <c r="AQ3">
-        <v>-6.416326530612245</v>
+        <v>-3.628750872295883</v>
       </c>
     </row>
   </sheetData>
